--- a/Arquivos_JML/dados_acareacoes_JML.xlsx
+++ b/Arquivos_JML/dados_acareacoes_JML.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,12 +466,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3320023486598</t>
+          <t>3320058971532</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
+          <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,44 +481,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Jhulia Januário de Andrade</t>
+          <t>marita</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+5531997100458</t>
+          <t>+5531975987221</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Avenida Antônio Carlos 302 fundos, Alvinópolis</t>
+          <t>rua alamenda ipe amarelo 25, Bom Jesus do Amparo</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pincéis de maquiagem Pincéis de maquiagem Multicolor Stand-Up Conjunto de maquiagem Inclui Pincel Blush Escova em Pó*1</t>
+          <t>Vestido Tule Longo Bordado Evangelica com elastex e Cinto Ajustavel Manga Princesa Tamanho M e G*1</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2.81</t>
+          <t>126.63</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-06-09 14:41:04</t>
+          <t>2026-09-18 12:54:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3320001465573</t>
+          <t>3320023976526</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -528,44 +528,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Simone Silva</t>
+          <t>Celia correia crispim</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+5531995373850</t>
+          <t>+5531997856215</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rua nico ferreira 332 Loja, Dionísio</t>
+          <t>Mgc120 2115 casa A, Nova Era</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Compressor 12V para Pneus | Carro, Moto, Bike e Bolas com Praticidade*1</t>
+          <t>Heyoo Capinha Capa para Samsung Luxo Premium, Suporte Magnetizado que Transforma o Uso Galaxy S25FE S25 S24 S23 EDGE ULTRA A56 A55 A54 A36 A35 A17 A16 A15*1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>5.72</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-06-08 17:07:31</t>
+          <t>2026-09-18 12:51:09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3320021488259</t>
+          <t>3320036985377</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
+          <t>(JML INT) PARLLON MATOS - ALVINOPOLIS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -575,44 +575,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Mateus Soares Moreira</t>
+          <t>Eliana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+5531983613645</t>
+          <t>+5531998918188</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>rua São Sebastião 83, Nova União</t>
+          <t>rua Francisco Repolez Gomes 311 casa, Sem-Peixe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sistema de alarme antifurto para motocicleta parada de partida do motor com controle, módulo chave e*1</t>
+          <t>Cinta Shorts Modeladora 2 em 1 Espartilho 3 Fechos 4 Barbatanas Controle Barriga Ajusavel Espartilho*1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-06-08 12:11:15</t>
+          <t>2026-09-18 12:49:03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3320091456627</t>
+          <t>3320072977968</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>(JML LOC) WASHINGTON TULIO ALMEIDA</t>
+          <t>(JML INT) YURI ANTONIO - PRATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -622,79 +622,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>evaaparecida616</t>
+          <t>Joice barbara</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+5531991540778</t>
+          <t>+5531998365741</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rua Boa vista 475, João Monlevade</t>
+          <t>seara s/n casa, São Domingos do Prata</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Depilador Recarregável Facial e Corporal para Ambos os Gêneros SU*1</t>
+          <t>Kit Conjunto 10 a 16 Infantil Menina Juvenil 6 peças Blogueirinha Shorts Blusa Roupa Feminino Verão*1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>72.32</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-06-08 12:11:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>3320033498478</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>(JML INT) FRANCISMAR LIMA- BOM JESUS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Fake Delivery</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Alessandra Fernandes</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>+5531984745324</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>avenida José Afonso Fernandes 645 casa, Nova União</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cinta Faixa 3m ou 5Metros Modeladora Abdominal*1</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.18</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-06-08 12:09:45</t>
+          <t>2026-09-18 09:36:43</t>
         </is>
       </c>
     </row>
